--- a/2026/PATXOT 512/Febrero/PATXOT 521 Febrero.xlsx
+++ b/2026/PATXOT 512/Febrero/PATXOT 521 Febrero.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\PATXOT 512\Febrero\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Downloads\patxot\febrerp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B8EE656-B5D7-44B8-84EC-DA1E10291E67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10FCEF34-E5B1-4ADF-B3BF-8882F0203A84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="detalle y gastos" sheetId="3" r:id="rId1"/>
@@ -18,16 +18,21 @@
     <sheet name="edesur" sheetId="5" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'detalle y gastos'!$A$1:$C$50</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'detalle y gastos'!$A$1:$C$49</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">edesur!$A$1:$H$15</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'prorrateo '!$A$1:$L$16</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="91">
   <si>
     <t>Dpto.</t>
   </si>
@@ -155,9 +160,6 @@
     <t>Valdez Norberto</t>
   </si>
   <si>
-    <t>Lean Cosenza</t>
-  </si>
-  <si>
     <t>Pereyra Amanda</t>
   </si>
   <si>
@@ -276,9 +278,6 @@
   </si>
   <si>
     <t>Prevision ordinaria</t>
-  </si>
-  <si>
-    <t>EDESUR:</t>
   </si>
   <si>
     <t>Honorarios Administracion</t>
@@ -299,16 +298,16 @@
 Del mismo modo, los saldos anteriores incluyen montos correspondientes a expensas adeudadas no solo del mes de diciembre, sino también de meses posteriores.</t>
   </si>
   <si>
-    <t>Ingresos que no corresponden al periodo liquidado</t>
-  </si>
-  <si>
     <t>LIQUIDACIÓN EXPENSAS FEBRERO 2026</t>
   </si>
   <si>
-    <t>AYSA - ENERO</t>
-  </si>
-  <si>
     <t>Edesur - ENERO</t>
+  </si>
+  <si>
+    <t>AYSA</t>
+  </si>
+  <si>
+    <t>Lucia Contartese</t>
   </si>
 </sst>
 </file>
@@ -1090,9 +1089,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="4" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="4" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1145,9 +1141,19 @@
     <xf numFmtId="3" fontId="9" fillId="3" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="9" fillId="3" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="9" fillId="3" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="14" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1157,12 +1163,6 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1193,10 +1193,9 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="4" fontId="14" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="14" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1277,9 +1276,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1317,9 +1316,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1352,9 +1351,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1387,9 +1403,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1566,17 +1599,17 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:F61"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A2:F60"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
-    <col min="2" max="2" width="40.33203125" customWidth="1"/>
-    <col min="3" max="3" width="16.44140625" customWidth="1"/>
-    <col min="4" max="4" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.28515625" customWidth="1"/>
+    <col min="3" max="3" width="16.42578125" customWidth="1"/>
+    <col min="4" max="4" width="12.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>17</v>
       </c>
@@ -1584,128 +1617,128 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
       <c r="B5" s="16"/>
       <c r="C5" s="2"/>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="87" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B7" s="17"/>
       <c r="C7" s="17"/>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="14" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="40" t="s">
         <v>11</v>
       </c>
       <c r="B16" s="31"/>
       <c r="C16" s="6"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="31" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B17" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="C17" s="90">
-        <v>35799</v>
-      </c>
-      <c r="D17" s="91"/>
+      <c r="C17" s="136">
+        <v>151038.56</v>
+      </c>
+      <c r="D17" s="90"/>
       <c r="F17" s="7"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="42"/>
       <c r="B18" s="43"/>
       <c r="C18" s="25">
         <f>SUM(C17:C17)</f>
-        <v>35799</v>
+        <v>151038.56</v>
       </c>
       <c r="D18" s="26"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="40" t="s">
         <v>18</v>
       </c>
       <c r="B19" s="41"/>
-      <c r="C19" s="92"/>
+      <c r="C19" s="91"/>
       <c r="D19" s="26"/>
     </row>
-    <row r="20" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="31" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B20" s="44"/>
-      <c r="C20" s="38">
+      <c r="C20" s="118">
         <v>37000</v>
       </c>
       <c r="D20" s="26"/>
       <c r="F20" s="13"/>
     </row>
-    <row r="21" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="31" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B21" s="44"/>
-      <c r="C21" s="136">
+      <c r="C21" s="118">
         <v>51187.02</v>
       </c>
       <c r="D21" s="26"/>
       <c r="F21" s="13"/>
     </row>
-    <row r="22" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="31" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B22" s="41"/>
       <c r="C22" s="39"/>
-      <c r="D22" s="93"/>
+      <c r="D22" s="92"/>
       <c r="E22" s="7"/>
       <c r="F22" s="13"/>
     </row>
-    <row r="23" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="42"/>
       <c r="B23" s="43"/>
       <c r="C23" s="25">
@@ -1714,51 +1747,51 @@
       </c>
       <c r="F23" s="13"/>
     </row>
-    <row r="24" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="35" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B24" s="35"/>
       <c r="C24" s="45">
         <f>+C23+C18</f>
-        <v>123986.01999999999</v>
+        <v>239225.58</v>
       </c>
       <c r="F24" s="13"/>
     </row>
-    <row r="25" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C25" s="26"/>
       <c r="F25" s="13"/>
     </row>
-    <row r="26" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
         <v>25</v>
       </c>
       <c r="C26" s="26"/>
       <c r="F26" s="13"/>
     </row>
-    <row r="27" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="31"/>
       <c r="B27" s="31"/>
       <c r="C27" s="38"/>
       <c r="F27" s="13"/>
     </row>
-    <row r="28" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" s="31"/>
       <c r="B28" s="31"/>
       <c r="C28" s="39"/>
       <c r="F28" s="13"/>
     </row>
-    <row r="29" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" s="31"/>
       <c r="B29" s="31"/>
       <c r="C29" s="39"/>
       <c r="F29" s="13"/>
     </row>
-    <row r="30" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C30" s="27"/>
       <c r="F30" s="13"/>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="14" t="s">
         <v>22</v>
       </c>
@@ -1769,211 +1802,201 @@
       </c>
       <c r="E31" s="7"/>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="20" t="s">
         <v>13</v>
       </c>
       <c r="B33" s="20"/>
       <c r="C33" s="21">
         <f>+C31+C24</f>
-        <v>123986.01999999999</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="35" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>239225.58</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="35" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="83" t="s">
         <v>19</v>
       </c>
       <c r="B35" s="84"/>
       <c r="C35" s="85"/>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="81" t="s">
         <v>8</v>
       </c>
       <c r="B36" s="2"/>
       <c r="C36" s="82">
-        <v>-782106.07639999967</v>
+        <v>-594990.1744239995</v>
       </c>
       <c r="D36" s="5"/>
       <c r="E36" s="5"/>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>7</v>
       </c>
       <c r="C37" s="18">
         <f>'prorrateo '!F15</f>
-        <v>1216661.4719760001</v>
+        <v>463282.77597850747</v>
       </c>
       <c r="D37" s="7"/>
       <c r="E37" s="7"/>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C38" s="46">
-        <v>-761194</v>
+        <f>-edesur!H1</f>
+        <v>-171431.43</v>
       </c>
       <c r="D38" s="7"/>
       <c r="E38" s="7"/>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>92</v>
+        <v>36</v>
       </c>
       <c r="C39" s="46">
-        <f>-(281988.92-122970.95)</f>
-        <v>-159017.96999999997</v>
-      </c>
-      <c r="D39" s="7"/>
-      <c r="E39" s="7"/>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
-        <v>36</v>
-      </c>
-      <c r="C40" s="46">
         <f>-C24</f>
-        <v>-123986.01999999999</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A41" s="22" t="s">
+        <v>-239225.58</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="B41" s="19"/>
-      <c r="C41" s="23">
-        <f>SUM(C36:C40)</f>
-        <v>-609642.59442399954</v>
-      </c>
-      <c r="D41" s="5"/>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A42" s="10"/>
-      <c r="B42" s="9"/>
-      <c r="C42" s="11"/>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A43" s="119" t="str">
+      <c r="B40" s="19"/>
+      <c r="C40" s="23">
+        <f>SUM(C36:C39)</f>
+        <v>-542364.40844549204</v>
+      </c>
+      <c r="D40" s="5"/>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="10"/>
+      <c r="B41" s="9"/>
+      <c r="C41" s="11"/>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="119" t="str">
         <f>'prorrateo '!A16:L16</f>
         <v>Atención: se han reliquidado todas las deudas correspondientes a cada unidad funcional, dejando reflejados los saldos reales de cada una.
 A partir de este mes se aplicarán intereses a quienes no abonen las expensas en tiempo y forma.
 La columna Ingresos registra pagos efectuados tanto durante el mes de enero como en meses anteriores. Por este motivo, en la caja general se han descontado aquellos pagos que no corresponden al período liquidado, a fin de evitar su doble contabilización, ya que los mismos fueron imputados oportunamente en expensas anteriores.
 Del mismo modo, los saldos anteriores incluyen montos correspondientes a expensas adeudadas no solo del mes de diciembre, sino también de meses posteriores.</v>
       </c>
+      <c r="B42" s="119"/>
+      <c r="C42" s="119"/>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="119"/>
       <c r="B43" s="119"/>
       <c r="C43" s="119"/>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="119"/>
       <c r="B44" s="119"/>
       <c r="C44" s="119"/>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="119"/>
       <c r="B45" s="119"/>
       <c r="C45" s="119"/>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="119"/>
       <c r="B46" s="119"/>
       <c r="C46" s="119"/>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="119"/>
       <c r="B47" s="119"/>
       <c r="C47" s="119"/>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="119"/>
       <c r="B48" s="119"/>
       <c r="C48" s="119"/>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" ht="81.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="119"/>
       <c r="B49" s="119"/>
       <c r="C49" s="119"/>
     </row>
-    <row r="50" spans="1:6" ht="81.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="119"/>
-      <c r="B50" s="119"/>
-      <c r="C50" s="119"/>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="10"/>
+      <c r="B50" s="9"/>
+      <c r="C50" s="11"/>
+      <c r="F50" s="47"/>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="10"/>
       <c r="B51" s="9"/>
       <c r="C51" s="11"/>
-      <c r="F51" s="47"/>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="10"/>
-      <c r="B52" s="9"/>
-      <c r="C52" s="11"/>
-    </row>
-    <row r="53" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A53" s="29" t="s">
+    </row>
+    <row r="52" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A52" s="29" t="s">
         <v>32</v>
       </c>
-      <c r="B53" s="30"/>
-      <c r="C53" s="33">
+      <c r="B52" s="30"/>
+      <c r="C52" s="33">
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" s="31" t="s">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" s="31" t="s">
         <v>35</v>
       </c>
-      <c r="B54" s="31"/>
-      <c r="C54" s="36">
+      <c r="B53" s="31"/>
+      <c r="C53" s="36">
         <f>-C31</f>
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="31"/>
+      <c r="B54" s="31"/>
+      <c r="C54" s="36"/>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="31"/>
       <c r="B55" s="31"/>
-      <c r="C55" s="36"/>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" s="31"/>
-      <c r="B56" s="31"/>
-      <c r="C56" s="37"/>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" s="35" t="s">
+      <c r="C55" s="37"/>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="B57" s="32"/>
-      <c r="C57" s="34">
-        <f>SUM(C53:C56)</f>
+      <c r="B56" s="32"/>
+      <c r="C56" s="34">
+        <f>SUM(C52:C55)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" s="9"/>
+      <c r="B57" s="9"/>
+      <c r="C57" s="9"/>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="9"/>
       <c r="B58" s="9"/>
       <c r="C58" s="9"/>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="9"/>
       <c r="B59" s="9"/>
       <c r="C59" s="9"/>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="9"/>
       <c r="B60" s="9"/>
       <c r="C60" s="9"/>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A61" s="9"/>
-      <c r="B61" s="9"/>
-      <c r="C61" s="9"/>
-    </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A43:C50"/>
+    <mergeCell ref="A42:C49"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B4" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -1991,579 +2014,563 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:N16"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.33203125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="5.28515625" style="1" customWidth="1"/>
     <col min="2" max="2" width="4" style="1" customWidth="1"/>
-    <col min="3" max="3" width="23.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.6640625" customWidth="1"/>
-    <col min="6" max="6" width="10.6640625" customWidth="1"/>
-    <col min="7" max="7" width="9.5546875" customWidth="1"/>
-    <col min="8" max="8" width="10.33203125" customWidth="1"/>
-    <col min="9" max="9" width="8.33203125" customWidth="1"/>
-    <col min="10" max="10" width="13.109375" customWidth="1"/>
-    <col min="11" max="11" width="11.44140625" customWidth="1"/>
-    <col min="12" max="12" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.44140625" style="12"/>
+    <col min="3" max="3" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.7109375" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" customWidth="1"/>
+    <col min="7" max="7" width="11.42578125" customWidth="1"/>
+    <col min="8" max="8" width="10.28515625" customWidth="1"/>
+    <col min="9" max="9" width="8.28515625" customWidth="1"/>
+    <col min="10" max="10" width="13.140625" customWidth="1"/>
+    <col min="11" max="11" width="11.42578125" customWidth="1"/>
+    <col min="12" max="12" width="12.85546875" customWidth="1"/>
+    <col min="14" max="14" width="11.42578125" style="12"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="95" t="s">
+    <row r="1" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="94" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="96"/>
+      <c r="B1" s="95"/>
       <c r="C1" s="26"/>
       <c r="D1" s="26"/>
       <c r="E1" s="27">
-        <v>109333.6</v>
+        <v>239225.58</v>
       </c>
       <c r="F1" s="26"/>
       <c r="G1" s="26"/>
-      <c r="H1" s="135" t="s">
-        <v>83</v>
-      </c>
-      <c r="I1" s="135"/>
-      <c r="J1" s="27">
-        <v>159017.97</v>
-      </c>
+      <c r="H1" s="122"/>
+      <c r="I1" s="122"/>
+      <c r="J1" s="27"/>
       <c r="K1" s="26"/>
       <c r="L1" s="26"/>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A2" s="97">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2" s="96">
         <f>'detalle y gastos'!B7</f>
         <v>0</v>
       </c>
-      <c r="B2" s="98"/>
-      <c r="C2" s="99"/>
-      <c r="D2" s="99"/>
-      <c r="E2" s="100"/>
-      <c r="F2" s="98"/>
-      <c r="G2" s="98"/>
-      <c r="H2" s="98"/>
-      <c r="I2" s="98"/>
-      <c r="J2" s="101"/>
-      <c r="K2" s="101"/>
-      <c r="L2" s="102"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="129" t="s">
+      <c r="B2" s="97"/>
+      <c r="C2" s="98"/>
+      <c r="D2" s="98"/>
+      <c r="E2" s="99"/>
+      <c r="F2" s="97"/>
+      <c r="G2" s="97"/>
+      <c r="H2" s="97"/>
+      <c r="I2" s="97"/>
+      <c r="J2" s="100"/>
+      <c r="K2" s="100"/>
+      <c r="L2" s="101"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3" s="130" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="130"/>
-      <c r="C3" s="125" t="s">
+      <c r="B3" s="131"/>
+      <c r="C3" s="126" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="127" t="s">
+      <c r="D3" s="128" t="s">
         <v>31</v>
       </c>
-      <c r="E3" s="103" t="s">
+      <c r="E3" s="102" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="103" t="s">
+      <c r="F3" s="102" t="s">
         <v>2</v>
       </c>
-      <c r="G3" s="125" t="s">
+      <c r="G3" s="126" t="s">
         <v>30</v>
       </c>
-      <c r="H3" s="125" t="s">
+      <c r="H3" s="126" t="s">
         <v>26</v>
       </c>
-      <c r="I3" s="121" t="s">
+      <c r="I3" s="124" t="s">
         <v>5</v>
       </c>
-      <c r="J3" s="133" t="s">
-        <v>80</v>
-      </c>
-      <c r="K3" s="125" t="s">
+      <c r="J3" s="134" t="s">
+        <v>79</v>
+      </c>
+      <c r="K3" s="126" t="s">
         <v>24</v>
       </c>
-      <c r="L3" s="104" t="s">
+      <c r="L3" s="103" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A4" s="131"/>
-      <c r="B4" s="132"/>
-      <c r="C4" s="126"/>
-      <c r="D4" s="128"/>
-      <c r="E4" s="105" t="s">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4" s="132"/>
+      <c r="B4" s="133"/>
+      <c r="C4" s="127"/>
+      <c r="D4" s="129"/>
+      <c r="E4" s="104" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="103" t="s">
+      <c r="F4" s="102" t="s">
         <v>27</v>
       </c>
-      <c r="G4" s="126"/>
-      <c r="H4" s="126"/>
-      <c r="I4" s="122"/>
-      <c r="J4" s="134"/>
-      <c r="K4" s="126"/>
-      <c r="L4" s="106" t="s">
+      <c r="G4" s="127"/>
+      <c r="H4" s="127"/>
+      <c r="I4" s="125"/>
+      <c r="J4" s="135"/>
+      <c r="K4" s="127"/>
+      <c r="L4" s="105" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="123">
+    <row r="5" spans="1:13" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="120">
         <v>1</v>
       </c>
-      <c r="B5" s="124"/>
+      <c r="B5" s="121"/>
       <c r="C5" s="48" t="s">
         <v>37</v>
       </c>
       <c r="D5" s="24"/>
       <c r="E5" s="86">
-        <v>46673.998480000002</v>
+        <v>24581.646949253736</v>
       </c>
       <c r="F5" s="86">
         <f>E5</f>
-        <v>46673.998480000002</v>
-      </c>
-      <c r="G5" s="107">
+        <v>24581.646949253736</v>
+      </c>
+      <c r="G5" s="106">
         <f>E5-F5</f>
         <v>0</v>
       </c>
-      <c r="H5" s="107">
+      <c r="H5" s="106">
         <f>IF(G5&gt;0,G5*6%,0)</f>
         <v>0</v>
       </c>
       <c r="I5" s="39">
         <v>13.8</v>
       </c>
-      <c r="J5" s="108">
+      <c r="J5" s="107">
         <f>E$1*I5/100</f>
-        <v>15088.036800000002</v>
-      </c>
-      <c r="K5" s="109">
+        <v>33013.130040000004</v>
+      </c>
+      <c r="K5" s="108">
         <f>edesur!H5</f>
-        <v>9493.6101492537327</v>
-      </c>
-      <c r="L5" s="110">
+        <v>10234.712238805971</v>
+      </c>
+      <c r="L5" s="109">
         <f>G5+H5+J5+K5</f>
-        <v>24581.646949253736</v>
+        <v>43247.842278805976</v>
       </c>
       <c r="M5" s="89"/>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A6" s="123">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A6" s="120">
         <v>2</v>
       </c>
-      <c r="B6" s="124"/>
+      <c r="B6" s="121"/>
       <c r="C6" s="48" t="s">
         <v>38</v>
       </c>
       <c r="D6" s="28"/>
       <c r="E6" s="86">
-        <v>93174.074720303732</v>
+        <v>158250.17389486523</v>
       </c>
       <c r="F6" s="86"/>
-      <c r="G6" s="107">
+      <c r="G6" s="106">
         <f t="shared" ref="G6:G14" si="0">E6-F6</f>
-        <v>93174.074720303732</v>
-      </c>
-      <c r="H6" s="107">
+        <v>158250.17389486523</v>
+      </c>
+      <c r="H6" s="106">
         <f t="shared" ref="H6:H14" si="1">IF(G6&gt;0,G6*6%,0)</f>
-        <v>5590.4444832182235</v>
+        <v>9495.0104336919139</v>
       </c>
       <c r="I6" s="39">
         <v>11.86</v>
       </c>
-      <c r="J6" s="108">
+      <c r="J6" s="107">
         <f t="shared" ref="J6:J14" si="2">E$1*I6/100</f>
-        <v>12966.964960000001</v>
-      </c>
-      <c r="K6" s="109">
+        <v>28372.153787999996</v>
+      </c>
+      <c r="K6" s="108">
         <f>edesur!H6</f>
-        <v>46518.689731343286</v>
-      </c>
-      <c r="L6" s="110">
+        <v>50150.089970149253</v>
+      </c>
+      <c r="L6" s="109">
         <f t="shared" ref="L6:L14" si="3">G6+H6+J6+K6</f>
-        <v>158250.17389486523</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="27" x14ac:dyDescent="0.3">
-      <c r="A7" s="123">
+        <v>246267.42808670638</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A7" s="120">
         <v>3</v>
       </c>
-      <c r="B7" s="124"/>
+      <c r="B7" s="121"/>
       <c r="C7" s="48" t="s">
         <v>38</v>
       </c>
       <c r="D7" s="28" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E7" s="86">
-        <f>404493.75+44569.42</f>
-        <v>449063.17</v>
+        <v>233997.93598388057</v>
       </c>
       <c r="F7" s="86">
-        <f>120000+50000+114600</f>
-        <v>284600</v>
-      </c>
-      <c r="G7" s="107">
+        <v>129800</v>
+      </c>
+      <c r="G7" s="106">
         <f t="shared" si="0"/>
-        <v>164463.16999999998</v>
-      </c>
-      <c r="H7" s="107">
+        <v>104197.93598388057</v>
+      </c>
+      <c r="H7" s="106">
         <f t="shared" si="1"/>
-        <v>9867.7901999999995</v>
+        <v>6251.876159032834</v>
       </c>
       <c r="I7" s="39">
         <v>12.46</v>
       </c>
-      <c r="J7" s="108">
+      <c r="J7" s="107">
         <f t="shared" si="2"/>
-        <v>13622.966560000003</v>
-      </c>
-      <c r="K7" s="109">
+        <v>29807.507267999998</v>
+      </c>
+      <c r="K7" s="108">
         <f>edesur!H7</f>
-        <v>46044.009223880596</v>
-      </c>
-      <c r="L7" s="110">
+        <v>49638.354358208955</v>
+      </c>
+      <c r="L7" s="109">
         <f t="shared" si="3"/>
-        <v>233997.93598388057</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A8" s="123">
+        <v>189895.67376912234</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A8" s="120">
         <v>4</v>
       </c>
-      <c r="B8" s="124"/>
+      <c r="B8" s="121"/>
       <c r="C8" s="48" t="s">
         <v>39</v>
       </c>
       <c r="D8" s="28" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E8" s="86">
-        <f>410990.58+104559.2</f>
-        <v>515549.78</v>
+        <v>248084.40294925377</v>
       </c>
       <c r="F8" s="86">
-        <f>128678+49000+128000</f>
-        <v>305678</v>
-      </c>
-      <c r="G8" s="107">
+        <v>128000</v>
+      </c>
+      <c r="G8" s="106">
         <f t="shared" si="0"/>
-        <v>209871.78000000003</v>
-      </c>
-      <c r="H8" s="107">
+        <v>120084.40294925377</v>
+      </c>
+      <c r="H8" s="106">
         <f t="shared" si="1"/>
-        <v>12592.306800000002</v>
+        <v>7205.0641769552258</v>
       </c>
       <c r="I8" s="39">
         <v>14.75</v>
       </c>
-      <c r="J8" s="108">
+      <c r="J8" s="107">
         <f t="shared" si="2"/>
-        <v>16126.706</v>
-      </c>
-      <c r="K8" s="109">
+        <v>35285.773049999996</v>
+      </c>
+      <c r="K8" s="108">
         <f>edesur!H8</f>
-        <v>9493.6101492537327</v>
-      </c>
-      <c r="L8" s="110">
+        <v>10234.712238805971</v>
+      </c>
+      <c r="L8" s="109">
         <f t="shared" si="3"/>
-        <v>248084.40294925377</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="123">
+        <v>172809.95241501497</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="120">
         <v>5</v>
       </c>
-      <c r="B9" s="124"/>
+      <c r="B9" s="121"/>
       <c r="C9" s="48" t="s">
         <v>40</v>
       </c>
       <c r="D9" s="28" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E9" s="86">
-        <f>65135.91+199803.65</f>
-        <v>264939.56</v>
-      </c>
-      <c r="F9" s="86">
-        <f>145436.21+54367.43+65136</f>
-        <v>264939.64</v>
-      </c>
-      <c r="G9" s="107">
+        <v>42049.050207761175</v>
+      </c>
+      <c r="F9" s="86"/>
+      <c r="G9" s="106">
         <f t="shared" si="0"/>
-        <v>-8.0000000016298145E-2</v>
-      </c>
-      <c r="H9" s="107">
+        <v>42049.050207761175</v>
+      </c>
+      <c r="H9" s="106">
+        <f t="shared" si="1"/>
+        <v>2522.9430124656706</v>
+      </c>
+      <c r="I9" s="39">
+        <v>12.41</v>
+      </c>
+      <c r="J9" s="107">
+        <f t="shared" si="2"/>
+        <v>29687.894477999998</v>
+      </c>
+      <c r="K9" s="108">
+        <v>0</v>
+      </c>
+      <c r="L9" s="109">
+        <f>G9+H9+J9+K9</f>
+        <v>74259.887698226841</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="120">
+        <v>6</v>
+      </c>
+      <c r="B10" s="121"/>
+      <c r="C10" s="48" t="s">
+        <v>41</v>
+      </c>
+      <c r="D10" s="28"/>
+      <c r="E10" s="86">
+        <v>314198.56462925376</v>
+      </c>
+      <c r="F10" s="86">
+        <v>150000</v>
+      </c>
+      <c r="G10" s="106">
+        <f t="shared" si="0"/>
+        <v>164198.56462925376</v>
+      </c>
+      <c r="H10" s="106">
+        <f t="shared" si="1"/>
+        <v>9851.9138777552253</v>
+      </c>
+      <c r="I10" s="39">
+        <v>12.48</v>
+      </c>
+      <c r="J10" s="107">
+        <f t="shared" si="2"/>
+        <v>29855.352384000002</v>
+      </c>
+      <c r="K10" s="108">
+        <f>edesur!H10</f>
+        <v>10234.712238805971</v>
+      </c>
+      <c r="L10" s="109">
+        <f t="shared" si="3"/>
+        <v>214140.54312981496</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="120">
+        <v>7</v>
+      </c>
+      <c r="B11" s="121"/>
+      <c r="C11" s="28" t="s">
+        <v>90</v>
+      </c>
+      <c r="D11" s="28"/>
+      <c r="E11" s="86">
+        <v>29457.925509253735</v>
+      </c>
+      <c r="F11" s="86">
+        <f t="shared" ref="F11:F14" si="4">E11</f>
+        <v>29457.925509253735</v>
+      </c>
+      <c r="G11" s="106">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H11" s="106">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I9" s="39">
-        <v>12.41</v>
-      </c>
-      <c r="J9" s="108">
-        <f t="shared" si="2"/>
-        <v>13568.29976</v>
-      </c>
-      <c r="K9" s="109">
-        <f>edesur!H9</f>
-        <v>28480.830447761193</v>
-      </c>
-      <c r="L9" s="110">
-        <f>G9+H9+J9+K9</f>
-        <v>42049.050207761175</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="123">
-        <v>6</v>
-      </c>
-      <c r="B10" s="124"/>
-      <c r="C10" s="48" t="s">
-        <v>41</v>
-      </c>
-      <c r="D10" s="28"/>
-      <c r="E10" s="86">
-        <f>44600+399309.33</f>
-        <v>443909.33</v>
-      </c>
-      <c r="F10" s="86">
-        <f>4150+26423+54675+85000+44601-F14</f>
-        <v>169324.31</v>
-      </c>
-      <c r="G10" s="107">
-        <f t="shared" si="0"/>
-        <v>274585.02</v>
-      </c>
-      <c r="H10" s="107">
-        <f t="shared" si="1"/>
-        <v>16475.101200000001</v>
-      </c>
-      <c r="I10" s="39">
-        <v>12.48</v>
-      </c>
-      <c r="J10" s="108">
-        <f t="shared" si="2"/>
-        <v>13644.833280000003</v>
-      </c>
-      <c r="K10" s="109">
-        <f>edesur!H10</f>
-        <v>9493.6101492537327</v>
-      </c>
-      <c r="L10" s="110">
-        <f t="shared" si="3"/>
-        <v>314198.56462925376</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="123">
-        <v>7</v>
-      </c>
-      <c r="B11" s="124"/>
-      <c r="C11" s="48" t="s">
-        <v>42</v>
-      </c>
-      <c r="D11" s="28"/>
-      <c r="E11" s="86">
-        <v>53678.783496000004</v>
-      </c>
-      <c r="F11" s="86">
-        <f t="shared" ref="F11:F14" si="4">E11</f>
-        <v>53678.783496000004</v>
-      </c>
-      <c r="G11" s="107">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H11" s="107">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
       <c r="I11" s="39">
         <v>18.260000000000002</v>
       </c>
-      <c r="J11" s="108">
+      <c r="J11" s="107">
         <f t="shared" si="2"/>
-        <v>19964.315360000004</v>
-      </c>
-      <c r="K11" s="109">
+        <v>43682.590908000006</v>
+      </c>
+      <c r="K11" s="108">
         <f>edesur!H11</f>
-        <v>9493.6101492537327</v>
-      </c>
-      <c r="L11" s="110">
+        <v>10234.712238805971</v>
+      </c>
+      <c r="L11" s="109">
         <f t="shared" si="3"/>
-        <v>29457.925509253735</v>
+        <v>53917.303146805978</v>
       </c>
       <c r="M11" s="89"/>
     </row>
-    <row r="12" spans="1:13" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="123" t="s">
-        <v>45</v>
-      </c>
-      <c r="B12" s="124"/>
+    <row r="12" spans="1:13" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="120" t="s">
+        <v>44</v>
+      </c>
+      <c r="B12" s="121"/>
       <c r="C12" s="48" t="str">
         <f>C9</f>
         <v>Grand Jorge</v>
       </c>
       <c r="D12" s="88" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E12" s="86">
-        <f>44137.05+2104.58</f>
-        <v>46241.630000000005</v>
-      </c>
-      <c r="F12" s="86">
-        <f>44137.05+2105</f>
-        <v>46242.05</v>
-      </c>
-      <c r="G12" s="107">
+        <v>1464.6502400000018</v>
+      </c>
+      <c r="F12" s="86"/>
+      <c r="G12" s="106">
         <f t="shared" si="0"/>
-        <v>-0.41999999999825377</v>
-      </c>
-      <c r="H12" s="107">
+        <v>1464.6502400000018</v>
+      </c>
+      <c r="H12" s="106">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>87.879014400000102</v>
       </c>
       <c r="I12" s="39">
         <v>1.34</v>
       </c>
-      <c r="J12" s="108">
+      <c r="J12" s="107">
         <f t="shared" si="2"/>
-        <v>1465.07024</v>
-      </c>
-      <c r="K12" s="109"/>
-      <c r="L12" s="110">
+        <v>3205.6227720000002</v>
+      </c>
+      <c r="K12" s="108"/>
+      <c r="L12" s="109">
         <f t="shared" si="3"/>
-        <v>1464.6502400000018</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A13" s="123" t="s">
-        <v>46</v>
-      </c>
-      <c r="B13" s="124"/>
+        <v>4758.1520264000019</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A13" s="120" t="s">
+        <v>45</v>
+      </c>
+      <c r="B13" s="121"/>
       <c r="C13" s="48" t="str">
         <f>C6</f>
         <v>Maceyle Gabriela</v>
       </c>
       <c r="D13" s="28"/>
       <c r="E13" s="86">
-        <v>41426.1</v>
+        <v>45354.86952</v>
       </c>
       <c r="F13" s="86"/>
-      <c r="G13" s="107">
+      <c r="G13" s="106">
         <f t="shared" si="0"/>
-        <v>41426.1</v>
-      </c>
-      <c r="H13" s="107">
+        <v>45354.86952</v>
+      </c>
+      <c r="H13" s="106">
         <f t="shared" si="1"/>
-        <v>2485.5659999999998</v>
+        <v>2721.2921711999998</v>
       </c>
       <c r="I13" s="39">
         <v>1.32</v>
       </c>
-      <c r="J13" s="108">
+      <c r="J13" s="107">
         <f t="shared" si="2"/>
-        <v>1443.20352</v>
-      </c>
-      <c r="K13" s="109"/>
-      <c r="L13" s="110">
+        <v>3157.7776559999998</v>
+      </c>
+      <c r="K13" s="108"/>
+      <c r="L13" s="109">
         <f t="shared" si="3"/>
-        <v>45354.86952</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="123" t="s">
-        <v>47</v>
-      </c>
-      <c r="B14" s="124"/>
+        <v>51233.939347200001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="120" t="s">
+        <v>46</v>
+      </c>
+      <c r="B14" s="121"/>
       <c r="C14" s="24" t="str">
         <f>C6</f>
         <v>Maceyle Gabriela</v>
       </c>
       <c r="D14" s="28" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E14" s="86">
-        <f>43451.53+2073.16</f>
-        <v>45524.69</v>
+        <v>1443.20352</v>
       </c>
       <c r="F14" s="86">
         <f t="shared" si="4"/>
-        <v>45524.69</v>
-      </c>
-      <c r="G14" s="107">
+        <v>1443.20352</v>
+      </c>
+      <c r="G14" s="106">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H14" s="107">
+      <c r="H14" s="106">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I14" s="39">
         <v>1.32</v>
       </c>
-      <c r="J14" s="108">
+      <c r="J14" s="107">
         <f t="shared" si="2"/>
-        <v>1443.20352</v>
-      </c>
-      <c r="K14" s="109"/>
-      <c r="L14" s="110">
+        <v>3157.7776559999998</v>
+      </c>
+      <c r="K14" s="108"/>
+      <c r="L14" s="109">
         <f t="shared" si="3"/>
-        <v>1443.20352</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="111" t="s">
+        <v>3157.7776559999998</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="110" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="112"/>
-      <c r="C15" s="113"/>
-      <c r="D15" s="113"/>
-      <c r="E15" s="114">
+      <c r="B15" s="111"/>
+      <c r="C15" s="112"/>
+      <c r="D15" s="112"/>
+      <c r="E15" s="113">
         <f>SUM(E5:E14)</f>
-        <v>2000181.1166963042</v>
-      </c>
-      <c r="F15" s="115">
+        <v>1098882.423403522</v>
+      </c>
+      <c r="F15" s="114">
         <f>SUM(F5:F14)</f>
-        <v>1216661.4719760001</v>
-      </c>
-      <c r="G15" s="115"/>
-      <c r="H15" s="116">
+        <v>463282.77597850747</v>
+      </c>
+      <c r="G15" s="114"/>
+      <c r="H15" s="115">
         <f>SUM(H5:H14)</f>
-        <v>47011.208683218225</v>
-      </c>
-      <c r="I15" s="117">
+        <v>38135.978845500875</v>
+      </c>
+      <c r="I15" s="116">
         <f t="shared" ref="I15" si="5">SUM(I5:I14)</f>
         <v>100</v>
       </c>
-      <c r="J15" s="118">
+      <c r="J15" s="117">
         <f>SUM(J5:J14)</f>
-        <v>109333.6</v>
-      </c>
-      <c r="K15" s="114">
+        <v>239225.58</v>
+      </c>
+      <c r="K15" s="113">
         <f>SUM(K5:K11)</f>
-        <v>159017.97</v>
-      </c>
-      <c r="L15" s="114">
+        <v>140727.29328358208</v>
+      </c>
+      <c r="L15" s="113">
         <f>SUM(L5:L14)</f>
-        <v>1098882.423403522</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" ht="217.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="120" t="s">
-        <v>88</v>
-      </c>
-      <c r="B16" s="120"/>
-      <c r="C16" s="120"/>
-      <c r="D16" s="120"/>
-      <c r="E16" s="120"/>
-      <c r="F16" s="120"/>
-      <c r="G16" s="120"/>
-      <c r="H16" s="120"/>
-      <c r="I16" s="120"/>
-      <c r="J16" s="120"/>
-      <c r="K16" s="120"/>
-      <c r="L16" s="120"/>
+        <v>1053688.4995540974</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="217.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="123" t="s">
+        <v>86</v>
+      </c>
+      <c r="B16" s="123"/>
+      <c r="C16" s="123"/>
+      <c r="D16" s="123"/>
+      <c r="E16" s="123"/>
+      <c r="F16" s="123"/>
+      <c r="G16" s="123"/>
+      <c r="H16" s="123"/>
+      <c r="I16" s="123"/>
+      <c r="J16" s="123"/>
+      <c r="K16" s="123"/>
+      <c r="L16" s="123"/>
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="K3:K4"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="A11:B11"/>
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="A14:B14"/>
@@ -2580,10 +2587,6 @@
     <mergeCell ref="C3:C4"/>
     <mergeCell ref="D3:D4"/>
     <mergeCell ref="A3:B4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="K3:K4"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="A11:B11"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -2594,87 +2597,87 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:M34"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="6" max="7" width="15.44140625" customWidth="1"/>
-    <col min="8" max="8" width="18.33203125" customWidth="1"/>
-    <col min="9" max="9" width="13.5546875" customWidth="1"/>
-    <col min="10" max="10" width="22.5546875" customWidth="1"/>
-    <col min="11" max="11" width="13.88671875" customWidth="1"/>
+    <col min="6" max="7" width="15.42578125" customWidth="1"/>
+    <col min="8" max="8" width="18.28515625" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" customWidth="1"/>
+    <col min="10" max="10" width="22.5703125" customWidth="1"/>
+    <col min="11" max="11" width="13.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B1" s="49" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C1" s="50" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D1" s="51"/>
       <c r="F1" t="s">
         <v>24</v>
       </c>
       <c r="G1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H1" s="80">
-        <v>159017.97</v>
+        <v>171431.43</v>
       </c>
       <c r="K1" s="52"/>
       <c r="L1" s="53"/>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="H2" s="54"/>
       <c r="I2" s="54"/>
       <c r="J2" s="54"/>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B3" s="55" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3" s="49" t="s">
         <v>52</v>
       </c>
-      <c r="C3" s="49" t="s">
+      <c r="D3" s="49" t="s">
+        <v>52</v>
+      </c>
+      <c r="E3" s="49" t="s">
         <v>53</v>
       </c>
-      <c r="D3" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="E3" s="49" t="s">
+      <c r="F3" s="49" t="s">
         <v>54</v>
       </c>
-      <c r="F3" s="49" t="s">
+      <c r="G3" s="49" t="s">
         <v>55</v>
       </c>
-      <c r="G3" s="49" t="s">
+      <c r="H3" s="56" t="s">
         <v>56</v>
-      </c>
-      <c r="H3" s="56" t="s">
-        <v>57</v>
       </c>
       <c r="I3" s="55"/>
       <c r="J3" s="55"/>
       <c r="K3" s="4"/>
       <c r="M3" s="57"/>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B4" s="55"/>
       <c r="C4" s="49" t="s">
+        <v>57</v>
+      </c>
+      <c r="D4" s="49" t="s">
         <v>58</v>
-      </c>
-      <c r="D4" s="49" t="s">
-        <v>59</v>
       </c>
       <c r="E4" s="49"/>
       <c r="F4" s="49"/>
       <c r="H4" s="58">
         <f>H1</f>
-        <v>159017.97</v>
+        <v>171431.43</v>
       </c>
       <c r="I4" s="58"/>
       <c r="J4" s="58"/>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B5" s="55">
         <v>1</v>
@@ -2697,7 +2700,7 @@
       <c r="G5" s="4"/>
       <c r="H5" s="59">
         <f>H4*(F5/100)</f>
-        <v>9493.6101492537327</v>
+        <v>10234.712238805971</v>
       </c>
       <c r="I5" s="55"/>
       <c r="J5" s="4"/>
@@ -2705,9 +2708,9 @@
       <c r="L5" s="60"/>
       <c r="M5" s="61"/>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B6" s="55">
         <v>2</v>
@@ -2730,7 +2733,7 @@
       <c r="G6" s="4"/>
       <c r="H6" s="59">
         <f>H4*(F6/100)</f>
-        <v>46518.689731343286</v>
+        <v>50150.089970149253</v>
       </c>
       <c r="I6" s="55"/>
       <c r="J6" s="4"/>
@@ -2738,9 +2741,9 @@
       <c r="L6" s="60"/>
       <c r="M6" s="61"/>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B7" s="55">
         <v>3</v>
@@ -2762,7 +2765,7 @@
       </c>
       <c r="H7" s="62">
         <f>H4*(F7/100)</f>
-        <v>46044.009223880596</v>
+        <v>49638.354358208955</v>
       </c>
       <c r="I7" s="49"/>
       <c r="J7" s="4"/>
@@ -2770,9 +2773,9 @@
       <c r="L7" s="60"/>
       <c r="M7" s="61"/>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B8" s="55">
         <v>4</v>
@@ -2795,7 +2798,7 @@
       <c r="G8" s="4"/>
       <c r="H8" s="59">
         <f>H4*(F8/100)</f>
-        <v>9493.6101492537327</v>
+        <v>10234.712238805971</v>
       </c>
       <c r="I8" s="55"/>
       <c r="J8" s="4"/>
@@ -2803,9 +2806,9 @@
       <c r="L8" s="60"/>
       <c r="M8" s="61"/>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B9" s="55">
         <v>5</v>
@@ -2828,7 +2831,7 @@
       <c r="G9" s="4"/>
       <c r="H9" s="59">
         <f>H4*(F9/100)</f>
-        <v>28480.830447761193</v>
+        <v>30704.136716417906</v>
       </c>
       <c r="I9" s="55"/>
       <c r="J9" s="4"/>
@@ -2836,9 +2839,9 @@
       <c r="L9" s="60"/>
       <c r="M9" s="61"/>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B10" s="55">
         <v>6</v>
@@ -2861,7 +2864,7 @@
       <c r="G10" s="4"/>
       <c r="H10" s="59">
         <f>H4*(F10/100)</f>
-        <v>9493.6101492537327</v>
+        <v>10234.712238805971</v>
       </c>
       <c r="I10" s="55"/>
       <c r="J10" s="4"/>
@@ -2869,9 +2872,9 @@
       <c r="L10" s="60"/>
       <c r="M10" s="61"/>
     </row>
-    <row r="11" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B11" s="55">
         <v>7</v>
@@ -2894,7 +2897,7 @@
       <c r="G11" s="4"/>
       <c r="H11" s="59">
         <f>H4*(F11/100)</f>
-        <v>9493.6101492537327</v>
+        <v>10234.712238805971</v>
       </c>
       <c r="I11" s="55"/>
       <c r="J11" s="4"/>
@@ -2902,7 +2905,7 @@
       <c r="L11" s="60"/>
       <c r="M11" s="61"/>
     </row>
-    <row r="12" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B12" s="63"/>
       <c r="C12" s="64">
         <f>SUM(C5:C11)</f>
@@ -2921,24 +2924,24 @@
         <v>100.00000000000003</v>
       </c>
       <c r="G12" s="26"/>
-      <c r="H12" s="94">
+      <c r="H12" s="93">
         <f>SUM(H5:H11)</f>
-        <v>159017.97</v>
+        <v>171431.43</v>
       </c>
       <c r="I12" s="63"/>
       <c r="J12" s="63"/>
       <c r="K12" s="63"/>
       <c r="L12" s="66"/>
     </row>
-    <row r="13" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C13" s="67"/>
       <c r="H13" s="55"/>
       <c r="I13" s="55"/>
       <c r="J13" s="55"/>
     </row>
-    <row r="14" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D14" s="68">
         <f>D12-C12</f>
@@ -2948,15 +2951,15 @@
       <c r="I14" s="55"/>
       <c r="J14" s="55"/>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H15" s="55"/>
       <c r="I15" s="55"/>
       <c r="J15" s="55"/>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B16" s="55"/>
       <c r="C16" s="49"/>
       <c r="D16" s="49"/>
@@ -2967,7 +2970,7 @@
       <c r="J16" s="49"/>
       <c r="K16" s="4"/>
     </row>
-    <row r="17" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B17" s="55"/>
       <c r="C17" s="49"/>
       <c r="D17" s="49"/>
@@ -2977,12 +2980,12 @@
       <c r="I17" s="58"/>
       <c r="J17" s="58"/>
     </row>
-    <row r="18" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="H18" s="55"/>
       <c r="I18" s="55"/>
       <c r="J18" s="55"/>
     </row>
-    <row r="19" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:13" x14ac:dyDescent="0.25">
       <c r="C19" s="69"/>
       <c r="D19" s="70"/>
       <c r="E19" s="70"/>
@@ -2995,10 +2998,10 @@
       <c r="L19" s="70"/>
       <c r="M19" s="72"/>
     </row>
-    <row r="20" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:13" x14ac:dyDescent="0.25">
       <c r="C20" s="73"/>
       <c r="E20" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H20" s="74">
         <f>D14</f>
@@ -3007,33 +3010,33 @@
       <c r="I20" s="74"/>
       <c r="J20" s="74"/>
       <c r="K20" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="M20" s="75"/>
     </row>
-    <row r="21" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:13" x14ac:dyDescent="0.25">
       <c r="C21" s="73"/>
       <c r="D21" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E21">
         <v>7</v>
       </c>
       <c r="F21" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G21">
         <v>197</v>
       </c>
       <c r="H21" t="s">
+        <v>72</v>
+      </c>
+      <c r="K21" t="s">
         <v>73</v>
       </c>
-      <c r="K21" t="s">
-        <v>74</v>
-      </c>
       <c r="M21" s="75"/>
     </row>
-    <row r="22" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C22" s="76"/>
       <c r="D22" s="77"/>
       <c r="E22" s="77"/>
@@ -3046,30 +3049,30 @@
       <c r="L22" s="77"/>
       <c r="M22" s="78"/>
     </row>
-    <row r="25" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:13" x14ac:dyDescent="0.25">
       <c r="K25" s="79" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="26" spans="2:13" x14ac:dyDescent="0.3">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="26" spans="2:13" x14ac:dyDescent="0.25">
       <c r="G26" s="4"/>
       <c r="K26" s="57"/>
     </row>
-    <row r="27" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:13" x14ac:dyDescent="0.25">
       <c r="I27" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J27" t="s">
         <v>4</v>
       </c>
       <c r="K27" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="28" spans="2:13" x14ac:dyDescent="0.3">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="28" spans="2:13" x14ac:dyDescent="0.25">
       <c r="G28" s="4"/>
       <c r="H28" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I28" s="4">
         <v>29829</v>
@@ -3082,31 +3085,31 @@
         <v>45829</v>
       </c>
     </row>
-    <row r="31" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:13" x14ac:dyDescent="0.25">
       <c r="J31" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K31">
         <v>117067</v>
       </c>
     </row>
-    <row r="32" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:13" x14ac:dyDescent="0.25">
       <c r="J32" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K32">
         <v>-55000</v>
       </c>
     </row>
-    <row r="33" spans="10:11" x14ac:dyDescent="0.3">
+    <row r="33" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J33" s="57" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K33">
         <v>43965</v>
       </c>
     </row>
-    <row r="34" spans="10:11" x14ac:dyDescent="0.3">
+    <row r="34" spans="10:11" x14ac:dyDescent="0.25">
       <c r="K34" s="51">
         <f>SUM(K31:K33)</f>
         <v>106032</v>
